--- a/cds_files/IowaState_CDS_2021-2022.xlsx
+++ b/cds_files/IowaState_CDS_2021-2022.xlsx
@@ -499,7 +499,7 @@
         <v>0.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.11</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="5">
